--- a/stories/arbres/ATOM-REL.PAR.002-02.xlsx
+++ b/stories/arbres/ATOM-REL.PAR.002-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Naël est au parc avec papa. Tina est sur le toboggan. Le bois est lisse. Naël a envie de glisser. Papa dit : on attend. L'autre finit, puis c'est mon tour. Puis mon tour. Naël attend près de l'échelle. Il compte les oiseaux. Tina glisse. Puis c'est le tour de Naël. Naël glisse. L'air est frais. Papa dit : tu as su attendre. Plus tard, à la maison, ils peignent. La peinture sent le fruit. Tina a le pinceau rouge. Naël se souvient. Il attend. Papa dit : puis mon tour. Tina pose le pinceau. Puis c'est le tour de Naël. Il peint une pomme. Même leçon, autre lieu. Attendre, puis jouer.</t>
+          <t>Naël est au parc avec papa. Tina est sur le toboggan. Le bois est lisse. Naël a envie de glisser. On attend. L'autre finit, puis c'est mon tour. Puis mon tour. Naël attend près de l'échelle. Il compte les oiseaux. Tina glisse. Puis c'est le tour de Naël. Naël glisse. L'air est frais. Tu as su attendre. Plus tard, à la maison, ils peignent. La peinture sent le fruit. Tina a le pinceau rouge. Naël se souvient. Il attend. Puis mon tour. Tina pose le pinceau. Puis c'est le tour de Naël. Il peint une pomme. Même leçon, autre lieu. Attendre, puis jouer.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Naël est au parc avec papa. Tina est sur le toboggan. Le bois est lisse. Naël a envie de glisser.
+papa|On attend. L'autre finit, puis c'est mon tour.
+narrateur|Puis mon tour. Naël attend près de l'échelle. Il compte les oiseaux. Tina glisse. Puis c'est le tour de Naël. Naël glisse. L'air est frais.
+papa|Tu as su attendre. Plus tard, à la maison, ils peignent.
+narrateur|La peinture sent le fruit. Tina a le pinceau rouge. Naël se souvient. Il attend.
+papa|Puis mon tour.
+narrateur|Tina pose le pinceau. Puis c'est le tour de Naël. Il peint une pomme. Même leçon, autre lieu. Attendre, puis jouer.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Tina joue encore. Que fait Naël ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Naël a attendu. Au toboggan, puis avec le pinceau. Puis c'était son tour.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1828,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Naël pose le pinceau. Papa range les pots.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1995,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2035,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.PAR.002-02.xlsx
+++ b/stories/arbres/ATOM-REL.PAR.002-02.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,11 @@
 narrateur|Tina pose le pinceau. Puis c'est le tour de Naël. Il peint une pomme. Même leçon, autre lieu. Attendre, puis jouer.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1509,7 @@
           <t>narrateur|Tina joue encore. Que fait Naël ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1670,6 +1681,7 @@
           <t>narrateur|Naël a attendu. Au toboggan, puis avec le pinceau. Puis c'était son tour.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1845,7 @@
           <t>narrateur|Naël pose le pinceau. Papa range les pots.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2000,6 +2013,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2018,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2042,6 +2056,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2243,6 +2271,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-REL.PAR.002-02.xlsx
+++ b/stories/arbres/ATOM-REL.PAR.002-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Naël attend, puis c'est son tour</t>
+          <t>Amir attend, puis c'est son tour</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>L'échelle du toboggan brille. Nina glisse. Amir attend, puis c'est son tour. Plus tard, à la cuisine, il attend encore le pinceau rouge.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Naël est au parc avec papa. Tina est sur le toboggan. Le bois est lisse. Naël a envie de glisser. On attend. L'autre finit, puis c'est mon tour. Puis mon tour. Naël attend près de l'échelle. Il compte les oiseaux. Tina glisse. Puis c'est le tour de Naël. Naël glisse. L'air est frais. Tu as su attendre. Plus tard, à la maison, ils peignent. La peinture sent le fruit. Tina a le pinceau rouge. Naël se souvient. Il attend. Puis mon tour. Tina pose le pinceau. Puis c'est le tour de Naël. Il peint une pomme. Même leçon, autre lieu. Attendre, puis jouer.</t>
+          <t>L'échelle du toboggan brille au soleil. Une fourmi marche sur le bois. Papa a posé le gilet sur le banc. Le parc sent la poussière chaude. Un oiseau tape trois coups dans un arbre. Tu as vu la fourmi, Amir ? Oui, papa. Elle va tout droit. Tout droit, vers l'ombre. En ce moment, Nina est en haut. Le bois du toboggan est lisse. Amir a envie de glisser. Moi aussi. On attend. L'autre finit, puis c'est mon tour. Puis mon tour. Amir attend près de l'échelle. Il compte les oiseaux. Un oiseau. Deux oiseaux. Tu attends. Bravo, Amir. Le soleil chauffe l'échelle. Amir pose une main sur le bois. Le bois est chaud, un peu lisse. Encore un peu. On reste près. J'attends. Oui. C'est du bon travail. Nina glisse. L'air est frais sur le bois. Ses pieds touchent le sable. Puis mon tour. Puis mon tour. Amir monte. Il glisse. L'air est frais sur ses joues. Tu as su attendre. C'est du bon travail. Le sable est chaud ? Un peu, papa. Plus tard, ils rentrent. La cuisine sent le fruit. Papa a sorti la peinture. On peint une pomme ? Oui. Nina a le pinceau rouge. Amir se souvient. Il attend. Puis mon tour. Puis mon tour. Il compte les pots. Un pot. Deux pots. Tu attends encore. Même geste, autre lieu. La peinture sent la pomme. Une goutte rouge attend sur le pot. Nina pose le pinceau. C'est ton tour. Puis c'est le tour d'Amir. Il peint une pomme ronde. Le rouge sent le fruit. Tu as attendu. Puis tu as joué. Bravo, Amir. La pomme est assez ronde ? Oui, papa. C'est bien.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,13 +1324,76 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Naël est au parc avec papa. Tina est sur le toboggan. Le bois est lisse. Naël a envie de glisser.
-papa|On attend. L'autre finit, puis c'est mon tour.
-narrateur|Puis mon tour. Naël attend près de l'échelle. Il compte les oiseaux. Tina glisse. Puis c'est le tour de Naël. Naël glisse. L'air est frais.
-papa|Tu as su attendre. Plus tard, à la maison, ils peignent.
-narrateur|La peinture sent le fruit. Tina a le pinceau rouge. Naël se souvient. Il attend.
+          <t>narrateur|L'échelle du toboggan brille au soleil.
+narrateur|Une fourmi marche sur le bois.
+narrateur|Papa a posé le gilet sur le banc.
+narrateur|Le parc sent la poussière chaude.
+narrateur|Un oiseau tape trois coups dans un arbre.
+papa|Tu as vu la fourmi, Amir ?
+enfant-m|Oui, papa.
+enfant-m|Elle va tout droit.
+papa|Tout droit, vers l'ombre.
+narrateur|En ce moment, Nina est en haut.
+narrateur|Le bois du toboggan est lisse.
+narrateur|Amir a envie de glisser.
+enfant-m|Moi aussi.
+papa|On attend.
+papa|L'autre finit, puis c'est mon tour.
+enfant-m|Puis mon tour.
+narrateur|Amir attend près de l'échelle.
+narrateur|Il compte les oiseaux.
+enfant-m|Un oiseau.
+enfant-m|Deux oiseaux.
+papa|Tu attends.
+papa|Bravo, Amir.
+narrateur|Le soleil chauffe l'échelle.
+narrateur|Amir pose une main sur le bois.
+narrateur|Le bois est chaud, un peu lisse.
+papa|Encore un peu.
+papa|On reste près.
+enfant-m|J'attends.
+papa|Oui.
+papa|C'est du bon travail.
+narrateur|Nina glisse.
+narrateur|L'air est frais sur le bois.
+narrateur|Ses pieds touchent le sable.
 papa|Puis mon tour.
-narrateur|Tina pose le pinceau. Puis c'est le tour de Naël. Il peint une pomme. Même leçon, autre lieu. Attendre, puis jouer.</t>
+enfant-m|Puis mon tour.
+narrateur|Amir monte.
+narrateur|Il glisse.
+narrateur|L'air est frais sur ses joues.
+papa|Tu as su attendre.
+papa|C'est du bon travail.
+papa|Le sable est chaud ?
+enfant-m|Un peu, papa.
+narrateur|Plus tard, ils rentrent.
+narrateur|La cuisine sent le fruit.
+narrateur|Papa a sorti la peinture.
+papa|On peint une pomme ?
+enfant-m|Oui.
+narrateur|Nina a le pinceau rouge.
+narrateur|Amir se souvient.
+narrateur|Il attend.
+papa|Puis mon tour.
+enfant-m|Puis mon tour.
+narrateur|Il compte les pots.
+enfant-m|Un pot.
+enfant-m|Deux pots.
+papa|Tu attends encore.
+papa|Même geste, autre lieu.
+narrateur|La peinture sent la pomme.
+narrateur|Une goutte rouge attend sur le pot.
+narrateur|Nina pose le pinceau.
+enfant-f|C'est ton tour.
+narrateur|Puis c'est le tour d'Amir.
+narrateur|Il peint une pomme ronde.
+narrateur|Le rouge sent le fruit.
+papa|Tu as attendu.
+papa|Puis tu as joué.
+papa|Bravo, Amir.
+papa|La pomme est assez ronde ?
+enfant-m|Oui, papa.
+papa|C'est bien.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1350,7 +1425,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Tina joue encore. Que fait Naël ?</t>
+          <t>Nina joue encore. Que fait Amir ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1506,7 +1581,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Tina joue encore. Que fait Naël ?</t>
+          <t>narrateur|Nina joue encore.
+narrateur|Que fait Amir ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1534,7 +1610,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Naël a attendu. Au toboggan, puis avec le pinceau. Puis c'était son tour.</t>
+          <t>Amir a attendu. Au toboggan, puis avec le pinceau. Puis c'était son tour. Tu as attendu. Puis ton tour. Bravo, Amir. C'est du bon travail. Le rouge va jusqu'au bord ? Presque. On attend. Puis on joue. La peinture brille un peu. La fourmi est loin, maintenant.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1678,7 +1754,19 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Naël a attendu. Au toboggan, puis avec le pinceau. Puis c'était son tour.</t>
+          <t>narrateur|Amir a attendu.
+narrateur|Au toboggan, puis avec le pinceau.
+narrateur|Puis c'était son tour.
+papa|Tu as attendu.
+papa|Puis ton tour.
+papa|Bravo, Amir.
+papa|C'est du bon travail.
+papa|Le rouge va jusqu'au bord ?
+enfant-m|Presque.
+papa|On attend.
+papa|Puis on joue.
+narrateur|La peinture brille un peu.
+narrateur|La fourmi est loin, maintenant.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1706,7 +1794,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Naël pose le pinceau. Papa range les pots.</t>
+          <t>Amir pose le pinceau. Papa range les pots. On rince le pinceau ? Oui, papa. L'eau devient un peu rose. Tes doigts ont du rouge. On les lave ? Oui. Le savon sent le citron. Merci d'avoir attendu. Puis c'était ton tour.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1842,7 +1930,17 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Naël pose le pinceau. Papa range les pots.</t>
+          <t>narrateur|Amir pose le pinceau.
+narrateur|Papa range les pots.
+papa|On rince le pinceau ?
+enfant-m|Oui, papa.
+narrateur|L'eau devient un peu rose.
+papa|Tes doigts ont du rouge.
+papa|On les lave ?
+enfant-m|Oui.
+narrateur|Le savon sent le citron.
+papa|Merci d'avoir attendu.
+papa|Puis c'était ton tour.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1870,7 +1968,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai attendu. Puis mon tour. Bravo. Tu as fait du bon travail. La pomme rouge sèche sur la feuille. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2010,7 +2108,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai attendu.
+enfant-m|Puis mon tour.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|La pomme rouge sèche sur la feuille.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2032,7 +2135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2070,6 +2173,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.PAR.002-02.xlsx
+++ b/stories/arbres/ATOM-REL.PAR.002-02.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>L'échelle du toboggan brille au soleil. Une fourmi marche sur le bois. Papa a posé le gilet sur le banc. Le parc sent la poussière chaude. Un oiseau tape trois coups dans un arbre. Tu as vu la fourmi, Amir ? Oui, papa. Elle va tout droit. Tout droit, vers l'ombre. En ce moment, Nina est en haut. Le bois du toboggan est lisse. Amir a envie de glisser. Moi aussi. On attend. L'autre finit, puis c'est mon tour. Puis mon tour. Amir attend près de l'échelle. Il compte les oiseaux. Un oiseau. Deux oiseaux. Tu attends. Bravo, Amir. Le soleil chauffe l'échelle. Amir pose une main sur le bois. Le bois est chaud, un peu lisse. Encore un peu. On reste près. J'attends. Oui. C'est du bon travail. Nina glisse. L'air est frais sur le bois. Ses pieds touchent le sable. Puis mon tour. Puis mon tour. Amir monte. Il glisse. L'air est frais sur ses joues. Tu as su attendre. C'est du bon travail. Le sable est chaud ? Un peu, papa. Plus tard, ils rentrent. La cuisine sent le fruit. Papa a sorti la peinture. On peint une pomme ? Oui. Nina a le pinceau rouge. Amir se souvient. Il attend. Puis mon tour. Puis mon tour. Il compte les pots. Un pot. Deux pots. Tu attends encore. Même geste, autre lieu. La peinture sent la pomme. Une goutte rouge attend sur le pot. Nina pose le pinceau. C'est ton tour. Puis c'est le tour d'Amir. Il peint une pomme ronde. Le rouge sent le fruit. Tu as attendu. Puis tu as joué. Bravo, Amir. La pomme est assez ronde ? Oui, papa. C'est bien.</t>
+          <t>L'échelle du toboggan brille au soleil. Une fourmi marche sur le bois. Papa a posé le gilet sur le banc. Le parc sent la poussière chaude. Un oiseau tape trois coups dans un arbre. Tu as vu la fourmi, Amir ? Oui, papa. Elle va tout droit. Tout droit, vers l'ombre. En ce moment, Nina est en haut. Le bois du toboggan est lisse. Amir a envie de glisser. Moi aussi. On attend. L'autre finit, puis c'est mon tour. Puis mon tour. Amir attend près de l'échelle. Il compte les oiseaux. Un oiseau. Deux oiseaux. Tu attends. Bravo, Amir. Le soleil chauffe l'échelle. Amir pose une main sur le bois. Le bois est chaud, un peu lisse. Encore un peu. On reste près. J'attends. Oui. Nina glisse. L'air est frais sur le bois. Ses pieds touchent le sable. Puis mon tour. Puis mon tour. Amir monte. Il glisse. L'air est frais sur ses joues. Tu as su attendre. Le sable est chaud ? Un peu, papa. Plus tard, ils rentrent. La cuisine sent le fruit. Papa a sorti la peinture. On peint une pomme ? Oui. Nina a le pinceau rouge. Amir se souvient. Il attend. Puis mon tour. Puis mon tour. Il compte les pots. Un pot. Deux pots. Tu attends encore. Même geste, autre lieu. La peinture sent la pomme. Une goutte rouge attend sur le pot. Nina pose le pinceau. C'est ton tour. Puis c'est le tour d'Amir. Il peint une pomme ronde. Le rouge sent le fruit. Tu as attendu. Puis tu as joué. Bravo, Amir. La pomme est assez ronde ? Oui, papa. C'est bien.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Naël est au parc avec papa. Tina est sur le toboggan. Le bois est lisse. Naël a envie de glisser. Papa dit : on attend. L'autre finit, puis c'est mon tour. Puis mon tour. Naël attend près de l'échelle. Il compte les oiseaux. Tina glisse. Puis c'est le tour de Naël. Naël glisse. L'air est frais. Papa dit : tu as su &lt;emphasis level="moderate"&gt;attendre&lt;/emphasis&gt;. Plus tard, à la maison, ils peignent. La peinture sent le fruit. Tina a le pinceau rouge. Naël se souvient. Il attend. Papa dit : puis mon tour. Tina pose le pinceau. Puis c'est le tour de Naël. Il peint une pomme. Même leçon, autre lieu. Attendre, puis jouer.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>L'échelle du toboggan brille au soleil. Une fourmi marche sur le bois. Papa a posé le gilet sur le banc. Le parc sent la poussière chaude. Un oiseau tape trois coups dans un arbre. Tu as vu la fourmi, Amir ? Oui, papa. Elle va tout droit. Tout droit, vers l'ombre. En ce moment, Nina est en haut. Le bois du toboggan est lisse. Amir a envie de glisser. Moi aussi. On attend. L'autre finit, puis c'est mon tour. Puis mon tour. Amir attend près de l'échelle. Il compte les oiseaux. Un oiseau. Deux oiseaux. Tu attends. Bravo, Amir. Le soleil chauffe l'échelle. Amir pose une main sur le bois. Le bois est chaud, un peu lisse. Encore un peu. On reste près. J'attends. Oui. Nina glisse. L'air est frais sur le bois. Ses pieds touchent le sable. Puis mon tour. Puis mon tour. Amir monte. Il glisse. L'air est frais sur ses joues. Tu as su attendre. Le sable est chaud ? Un peu, papa. Plus tard, ils rentrent. La cuisine sent le fruit. Papa a sorti la peinture. On peint une pomme ? Oui. Nina a le pinceau rouge. Amir se souvient. Il attend. Puis mon tour. Puis mon tour. Il compte les pots. Un pot. Deux pots. Tu attends encore. Même geste, autre lieu. La peinture sent la pomme. Une goutte rouge attend sur le pot. Nina pose le pinceau. C'est ton tour. Puis c'est le tour d'Amir. Il peint une pomme ronde. Le rouge sent le fruit. Tu as attendu. Puis tu as joué. Bravo, Amir. La pomme est assez ronde ? Oui, papa. C'est bien.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1353,7 +1353,6 @@
 papa|On reste près.
 enfant-m|J'attends.
 papa|Oui.
-papa|C'est du bon travail.
 narrateur|Nina glisse.
 narrateur|L'air est frais sur le bois.
 narrateur|Ses pieds touchent le sable.
@@ -1363,7 +1362,6 @@
 narrateur|Il glisse.
 narrateur|L'air est frais sur ses joues.
 papa|Tu as su attendre.
-papa|C'est du bon travail.
 papa|Le sable est chaud ?
 enfant-m|Un peu, papa.
 narrateur|Plus tard, ils rentrent.
@@ -1430,7 +1428,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Tina joue encore. Que fait Naël ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina joue encore. Que fait Amir ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1585,7 +1583,6 @@
 narrateur|Que fait Amir ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1610,12 +1607,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Amir a attendu. Au toboggan, puis avec le pinceau. Puis c'était son tour. Tu as attendu. Puis ton tour. Bravo, Amir. C'est du bon travail. Le rouge va jusqu'au bord ? Presque. On attend. Puis on joue. La peinture brille un peu. La fourmi est loin, maintenant.</t>
+          <t>Amir a attendu. Au toboggan, puis avec le pinceau. Puis c'était son tour. Tu as attendu. Puis ton tour. Bravo, Amir. Le rouge va jusqu'au bord ? Presque. On attend. Puis on joue. La peinture brille un peu. La fourmi est loin, maintenant.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Naël a attendu. Au toboggan, &lt;emphasis level="moderate"&gt;puis&lt;/emphasis&gt; avec le pinceau. Puis c'était son tour.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir a attendu. Au toboggan, puis avec le pinceau. Puis c'était son tour. Tu as attendu. Puis ton tour. Bravo, Amir. Le rouge va jusqu'au bord ? Presque. On attend. Puis on joue. La peinture brille un peu. La fourmi est loin, maintenant.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1760,7 +1757,6 @@
 papa|Tu as attendu.
 papa|Puis ton tour.
 papa|Bravo, Amir.
-papa|C'est du bon travail.
 papa|Le rouge va jusqu'au bord ?
 enfant-m|Presque.
 papa|On attend.
@@ -1769,7 +1765,6 @@
 narrateur|La fourmi est loin, maintenant.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1799,7 +1794,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Naël pose le pinceau. Papa range les pots.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir pose le pinceau. Papa range les pots. On rince le pinceau ? Oui, papa. L'eau devient un peu rose. Tes doigts ont du rouge. On les lave ? Oui. Le savon sent le citron. Merci d'avoir attendu. Puis c'était ton tour.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1943,7 +1938,6 @@
 papa|Puis c'était ton tour.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1968,12 +1962,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai attendu. Puis mon tour. Bravo. Tu as fait du bon travail. La pomme rouge sèche sur la feuille. L'histoire est finie.</t>
+          <t>J'ai attendu. Puis mon tour. Bravo. La pomme rouge sèche sur la feuille.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai attendu. Puis mon tour. Bravo. La pomme rouge sèche sur la feuille.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2111,12 +2105,9 @@
           <t>enfant-m|J'ai attendu.
 enfant-m|Puis mon tour.
 papa|Bravo.
-papa|Tu as fait du bon travail.
-narrateur|La pomme rouge sèche sur la feuille.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|La pomme rouge sèche sur la feuille.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2135,7 +2126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2180,6 +2171,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.PAR.002-02.xlsx
+++ b/stories/arbres/ATOM-REL.PAR.002-02.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Naël, Tina, papa</t>
+          <t>Amir, Nina, papa</t>
         </is>
       </c>
     </row>
